--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2739" uniqueCount="506">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -444,33 +444,220 @@
     <t>Observation.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Auteur de l’observation</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document)
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.url</t>
+  </si>
+  <si>
+    <t>Observation.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Observation.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Observation.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -478,6 +665,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -588,9 +778,6 @@
     <t>final</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
@@ -613,10 +800,6 @@
   </si>
   <si>
     <t>Observation.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Classification of  type of observation</t>
@@ -859,13 +1042,6 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:extension.url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -876,277 +1052,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Observation.performer.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
-</t>
-  </si>
-  <si>
-    <t>Auteur de l’observation</t>
-  </si>
-  <si>
-    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode</t>
-  </si>
-  <si>
-    <t>typeCode</t>
-  </si>
-  <si>
-    <t>Type de participation</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor</t>
-  </si>
-  <si>
-    <t>actor</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document)
-</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.url</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Observation.performer.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>Observation.performer.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>Observation.performer.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>Observation.performer.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1200,6 +1105,9 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -1416,6 +1324,12 @@
   </si>
   <si>
     <t>Observation.referenceRange.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -2006,11 +1920,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP77"/>
+  <dimension ref="A1:AP71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.22265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.44921875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.80859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -3027,7 +2941,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3046,17 +2960,15 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>82</v>
@@ -3093,16 +3005,14 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>143</v>
@@ -3129,7 +3039,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3143,11 +3053,13 @@
         <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3160,26 +3072,22 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3227,7 +3135,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3236,7 +3144,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>144</v>
@@ -3251,7 +3159,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3260,12 +3168,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3273,33 +3181,31 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3347,34 +3253,34 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3382,18 +3288,18 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>81</v>
@@ -3405,21 +3311,19 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>164</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3455,19 +3359,19 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3479,19 +3383,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3502,21 +3406,23 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3525,20 +3431,18 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3587,7 +3491,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3599,19 +3503,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3620,12 +3524,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3633,35 +3537,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3670,7 +3570,7 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>82</v>
@@ -3685,13 +3585,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3709,10 +3609,10 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>93</v>
@@ -3721,22 +3621,22 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3744,10 +3644,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3758,7 +3658,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
@@ -3770,20 +3670,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>193</v>
+        <v>139</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3807,31 +3703,31 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3843,7 +3739,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3855,25 +3751,25 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3883,38 +3779,36 @@
         <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3929,13 +3823,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3953,7 +3847,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>93</v>
@@ -3965,33 +3859,33 @@
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>216</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3999,35 +3893,31 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>219</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -4036,7 +3926,7 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>82</v>
@@ -4051,13 +3941,11 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -4075,7 +3963,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4090,19 +3978,19 @@
         <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>225</v>
+        <v>136</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -4110,12 +3998,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>82</v>
       </c>
@@ -4124,7 +4014,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -4133,20 +4023,18 @@
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4195,7 +4083,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>162</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4207,7 +4095,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4216,13 +4104,13 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4230,14 +4118,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>234</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4253,23 +4141,19 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>235</v>
+        <v>153</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>236</v>
+        <v>154</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4317,7 +4201,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>156</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4329,69 +4213,65 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>242</v>
+        <v>157</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>244</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>244</v>
+        <v>168</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>246</v>
+        <v>138</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>247</v>
+        <v>139</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4427,46 +4307,46 @@
         <v>82</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>244</v>
+        <v>162</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4474,10 +4354,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4485,7 +4365,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>93</v>
@@ -4497,19 +4377,19 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>256</v>
+        <v>107</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>257</v>
+        <v>171</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>258</v>
+        <v>172</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>259</v>
+        <v>173</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4517,7 +4397,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>82</v>
@@ -4559,10 +4439,10 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>255</v>
+        <v>174</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>93</v>
@@ -4571,7 +4451,7 @@
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>82</v>
@@ -4580,13 +4460,13 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>261</v>
+        <v>136</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4594,10 +4474,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>176</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4608,30 +4488,28 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>264</v>
+        <v>190</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>265</v>
+        <v>177</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>266</v>
+        <v>178</v>
       </c>
       <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4667,23 +4545,25 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>182</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4692,19 +4572,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4712,18 +4592,20 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>274</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>93</v>
@@ -4738,13 +4620,13 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>275</v>
+        <v>138</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>276</v>
+        <v>139</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>277</v>
+        <v>140</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4795,19 +4677,19 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>278</v>
+        <v>162</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -4819,7 +4701,7 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -4830,21 +4712,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>280</v>
+        <v>193</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>280</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4856,17 +4738,15 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4903,31 +4783,31 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>284</v>
+        <v>156</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -4939,7 +4819,7 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>279</v>
+        <v>157</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4950,14 +4830,12 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>285</v>
+        <v>194</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4966,7 +4844,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4978,13 +4856,13 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>287</v>
+        <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>288</v>
+        <v>139</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>289</v>
+        <v>140</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5023,19 +4901,19 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>284</v>
+        <v>162</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5070,10 +4948,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>290</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5081,7 +4959,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>93</v>
@@ -5096,22 +4974,24 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>275</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>276</v>
+        <v>171</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5153,10 +5033,10 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>278</v>
+        <v>174</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>93</v>
@@ -5177,7 +5057,7 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>136</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5188,10 +5068,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>196</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>293</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5199,10 +5079,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5214,13 +5094,13 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>295</v>
+        <v>177</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>296</v>
+        <v>178</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5259,31 +5139,31 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>284</v>
+        <v>182</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5295,7 +5175,7 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5306,14 +5186,12 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>297</v>
+        <v>198</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5334,22 +5212,24 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>295</v>
+        <v>171</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>82</v>
@@ -5391,19 +5271,19 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>284</v>
+        <v>174</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5415,7 +5295,7 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5426,10 +5306,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>201</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5440,7 +5320,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5452,13 +5332,13 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>177</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
+        <v>178</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5509,7 +5389,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>182</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5521,7 +5401,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5533,7 +5413,7 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>136</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5544,42 +5424,46 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>204</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5615,19 +5499,19 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>284</v>
+        <v>210</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5651,7 +5535,7 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5662,10 +5546,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>303</v>
+        <v>211</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>211</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5673,10 +5557,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5685,27 +5569,27 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>212</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>305</v>
+        <v>213</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>82</v>
@@ -5747,34 +5631,34 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>211</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5782,21 +5666,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>310</v>
+        <v>220</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5805,19 +5689,21 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>113</v>
+        <v>222</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>311</v>
+        <v>223</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>312</v>
+        <v>224</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5826,7 +5712,7 @@
         <v>82</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>82</v>
@@ -5841,11 +5727,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5863,13 +5751,13 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>220</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -5878,16 +5766,16 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5898,23 +5786,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>229</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5923,18 +5809,20 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>139</v>
+        <v>231</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>232</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5983,7 +5871,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>284</v>
+        <v>229</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5995,19 +5883,19 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6016,12 +5904,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>238</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>238</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6029,31 +5917,35 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>275</v>
+        <v>113</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6062,7 +5954,7 @@
         <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>82</v>
@@ -6077,13 +5969,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6101,10 +5993,10 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>238</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>93</v>
@@ -6113,22 +6005,22 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6136,10 +6028,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>320</v>
+        <v>251</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>251</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6150,7 +6042,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6162,16 +6054,20 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>252</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6195,31 +6091,31 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6231,7 +6127,7 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6243,25 +6139,25 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>321</v>
+        <v>260</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6271,36 +6167,38 @@
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>306</v>
+        <v>263</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>82</v>
@@ -6315,13 +6213,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6339,7 +6237,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>308</v>
+        <v>260</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>93</v>
@@ -6351,33 +6249,33 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>136</v>
+        <v>273</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>276</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>276</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6385,31 +6283,35 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>277</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6457,7 +6359,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>315</v>
+        <v>276</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6472,19 +6374,19 @@
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>136</v>
+        <v>284</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6492,23 +6394,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>323</v>
+        <v>286</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6517,18 +6417,20 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>139</v>
+        <v>287</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6577,7 +6479,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6589,7 +6491,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6598,13 +6500,13 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6612,14 +6514,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6635,19 +6537,23 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6695,7 +6601,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6707,65 +6613,69 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>139</v>
+        <v>305</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6801,46 +6711,46 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6848,10 +6758,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6859,7 +6769,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
@@ -6871,19 +6781,19 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>315</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6891,7 +6801,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>82</v>
@@ -6933,10 +6843,10 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>93</v>
@@ -6945,7 +6855,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6954,13 +6864,13 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>136</v>
+        <v>320</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6968,10 +6878,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6982,7 +6892,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6991,19 +6901,21 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7051,13 +6963,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7066,27 +6978,27 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>136</v>
+        <v>329</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>331</v>
@@ -7103,33 +7015,35 @@
         <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>332</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7171,45 +7085,45 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>136</v>
+        <v>340</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7220,7 +7134,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7232,16 +7146,20 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>335</v>
+        <v>190</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7265,13 +7183,13 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7289,7 +7207,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7298,7 +7216,7 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
@@ -7310,10 +7228,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>136</v>
+        <v>351</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7322,16 +7240,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7341,27 +7259,29 @@
         <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>275</v>
+        <v>190</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7385,13 +7305,11 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7409,16 +7327,16 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>105</v>
@@ -7427,27 +7345,27 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>136</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7458,30 +7376,32 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>364</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7505,13 +7425,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7529,13 +7449,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -7550,10 +7470,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>136</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7562,12 +7482,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7581,25 +7501,25 @@
         <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7625,13 +7545,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7649,7 +7569,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7667,27 +7587,27 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7701,27 +7621,29 @@
         <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>275</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7745,13 +7667,11 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7769,7 +7689,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7790,10 +7710,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>136</v>
+        <v>388</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7802,12 +7722,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7815,35 +7735,33 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7891,7 +7809,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7900,7 +7818,7 @@
         <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -7909,27 +7827,27 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>371</v>
+        <v>397</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7952,20 +7870,18 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>192</v>
+        <v>399</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7989,13 +7905,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8013,7 +7929,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8022,7 +7938,7 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -8031,41 +7947,41 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
@@ -8074,19 +7990,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>192</v>
+        <v>408</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8111,11 +8027,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8133,7 +8051,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8145,33 +8063,33 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>413</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8182,10 +8100,10 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -8194,20 +8112,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>393</v>
+        <v>153</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>394</v>
+        <v>154</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8255,19 +8169,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>392</v>
+        <v>156</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8276,10 +8190,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>399</v>
+        <v>157</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8288,26 +8202,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8316,16 +8230,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>403</v>
+        <v>208</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8351,13 +8265,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8375,80 +8289,80 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>400</v>
+        <v>162</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>408</v>
+        <v>157</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I54" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I54" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>413</v>
+        <v>208</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>414</v>
+        <v>209</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8473,11 +8387,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8495,19 +8411,19 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8516,10 +8432,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>417</v>
+        <v>136</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8530,10 +8446,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8556,17 +8472,15 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8615,7 +8529,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8624,7 +8538,7 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>105</v>
@@ -8633,27 +8547,27 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8676,17 +8590,15 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8735,7 +8647,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8744,7 +8656,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -8753,19 +8665,19 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -8784,7 +8696,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8796,19 +8708,19 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8833,13 +8745,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8863,25 +8775,25 @@
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>442</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>444</v>
+        <v>361</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8906,7 +8818,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -8918,16 +8830,20 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>275</v>
+        <v>190</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>276</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -8951,13 +8867,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8975,31 +8891,31 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>278</v>
+        <v>445</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>279</v>
+        <v>361</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9010,21 +8926,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9036,18 +8952,18 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>139</v>
+        <v>453</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>140</v>
+        <v>454</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9095,19 +9011,19 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>284</v>
+        <v>452</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9119,7 +9035,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>279</v>
+        <v>457</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9130,46 +9046,42 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9217,19 +9129,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9238,10 +9150,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>136</v>
+        <v>461</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9252,10 +9164,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9266,7 +9178,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9275,18 +9187,20 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9335,16 +9249,16 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9356,10 +9270,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9370,10 +9284,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9384,7 +9298,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9393,18 +9307,20 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9453,16 +9369,16 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9474,10 +9390,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9488,10 +9404,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9502,7 +9418,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9511,22 +9427,22 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>192</v>
+        <v>408</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9551,13 +9467,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9575,13 +9491,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -9593,13 +9509,13 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>390</v>
+        <v>481</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9610,10 +9526,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9624,7 +9540,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9636,20 +9552,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>473</v>
+        <v>154</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9673,13 +9585,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9697,31 +9609,31 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>472</v>
+        <v>156</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>390</v>
+        <v>157</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9732,21 +9644,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9758,18 +9670,18 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>480</v>
+        <v>138</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>481</v>
+        <v>418</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -9817,19 +9729,19 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>479</v>
+        <v>162</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -9841,7 +9753,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>484</v>
+        <v>157</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9852,42 +9764,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>275</v>
+        <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>486</v>
+        <v>422</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -9935,19 +9851,19 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>485</v>
+        <v>424</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -9956,10 +9872,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>488</v>
+        <v>136</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -9970,10 +9886,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9981,10 +9897,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -9996,18 +9912,20 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>490</v>
+        <v>190</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10031,13 +9949,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10055,13 +9973,13 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
@@ -10073,16 +9991,16 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>494</v>
+        <v>272</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>495</v>
+        <v>273</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>82</v>
@@ -10090,10 +10008,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10104,7 +10022,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10116,18 +10034,20 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>499</v>
+        <v>334</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10175,13 +10095,13 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
@@ -10193,27 +10113,27 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>494</v>
+        <v>339</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>501</v>
+        <v>340</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10224,7 +10144,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10233,22 +10153,22 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>437</v>
+        <v>190</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>506</v>
+        <v>346</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10273,13 +10193,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10297,16 +10217,16 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10318,10 +10238,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>507</v>
+        <v>136</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>508</v>
+        <v>351</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10332,21 +10252,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10358,16 +10278,20 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>275</v>
+        <v>190</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>276</v>
+        <v>500</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10391,13 +10315,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10415,49 +10339,49 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>278</v>
+        <v>499</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>279</v>
+        <v>361</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10476,18 +10400,20 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>140</v>
+        <v>504</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>281</v>
+        <v>505</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10535,7 +10461,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>284</v>
+        <v>503</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10547,7 +10473,7 @@
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -10556,752 +10482,20 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>279</v>
+        <v>415</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP77" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP77">
+  <autoFilter ref="A1:AP71">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11311,7 +10505,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI76">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
